--- a/PCB/STM32G491CET6 Pins.xlsx
+++ b/PCB/STM32G491CET6 Pins.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\OTC\OTCboard\PCB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tonychen/Desktop/Working/OTCboard/PCB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0DE0D60-F158-4D8F-9EB9-DE30914017E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF473CB-E682-9C46-BD52-4D6D47A60CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="1400" windowWidth="6960" windowHeight="8780" xr2:uid="{2300AD52-4512-4A2D-B69E-82F1F727CC1A}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{2300AD52-4512-4A2D-B69E-82F1F727CC1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -580,9 +580,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDD25E2-BD92-4CBC-A8F9-92DF97977864}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -625,7 +625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -649,7 +649,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <f>A3+1</f>
         <v>3</v>
@@ -673,7 +673,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <f>A4+1</f>
         <v>4</v>
@@ -697,7 +697,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <f>A5+1</f>
         <v>5</v>
@@ -715,7 +715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <f>A6+1</f>
         <v>6</v>
@@ -733,7 +733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" ref="A8:A49" si="0">A7+1</f>
         <v>7</v>
@@ -745,7 +745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -763,7 +763,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -781,7 +781,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -799,7 +799,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -817,7 +817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -829,217 +829,217 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1047,5 +1047,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>